--- a/datos_productividad.xlsx
+++ b/datos_productividad.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -965,6 +965,41 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-12 08:39</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stryker</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CW2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>444</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
